--- a/results_two/results_two.xlsx
+++ b/results_two/results_two.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leticiadupleich/Desktop/Capstone/LeticiaCapstone/results_two/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64C2E2D-D84D-C342-91F7-B236D03788A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B340B133-6927-6B4D-B163-70F82A50E722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{F1D71396-1DC3-294D-A1BC-F6200886B423}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" activeTab="3" xr2:uid="{F1D71396-1DC3-294D-A1BC-F6200886B423}"/>
   </bookViews>
   <sheets>
     <sheet name="time_overall" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
     <t>Two CPU Time Polars</t>
   </si>
   <si>
-    <t>Elapsed Time</t>
-  </si>
-  <si>
     <t>CPU Time</t>
   </si>
   <si>
@@ -135,6 +132,9 @@
   </si>
   <si>
     <t>Appointments per Patient  (SQL)</t>
+  </si>
+  <si>
+    <t>Execution Time</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1562,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Elapsed Time</c:v>
+                  <c:v>Execution Time</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5950,7 +5950,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Elapsed Time</c:v>
+                  <c:v>Execution Time</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7044,7 +7044,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Elapsed Time</c:v>
+                  <c:v>Execution Time</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8130,7 +8130,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Elapsed Time</c:v>
+                  <c:v>Execution Time</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -15081,18 +15081,18 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3">
         <row r="2">
           <cell r="A2" t="str">
-            <v>Elapsed Time</v>
+            <v>Execution Time</v>
           </cell>
           <cell r="B2" t="str">
             <v>CPU Time</v>
           </cell>
           <cell r="G2" t="str">
-            <v>Elapsed Time</v>
+            <v>Execution Time</v>
           </cell>
           <cell r="H2" t="str">
             <v>CPU Time</v>
@@ -16485,12 +16485,12 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -19555,48 +19555,48 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="19"/>
       <c r="D1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" s="6"/>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="6"/>
       <c r="J1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>25</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>25</v>
-      </c>
       <c r="G2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="21" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="21" t="s">
         <v>24</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
